--- a/schematic-design/Partslist_Group_PE04_2 - With HSRW.xlsx
+++ b/schematic-design/Partslist_Group_PE04_2 - With HSRW.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ad1c0a53281c2ab/Documents/University/Studies/Sem 5/Practical Electronics/pe04/schematic-design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\pe04\schematic-design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{23A68183-9883-4898-B30F-B2C1DE7AC4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{394C5F17-CE64-48EF-A993-8447C8068017}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEBE582-9EB0-4947-90E2-B5CA8B45C980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-10800" yWindow="6720" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parts" sheetId="5" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="127">
   <si>
     <t>Link</t>
   </si>
@@ -267,15 +267,6 @@
     <t>DFRobot</t>
   </si>
   <si>
-    <t>https://www.mouser.de/ProductDetail/Same-Sky/UJ2-B-HR-G-TH?qs=HoCaDK9Nz5cuzuu5C%2FN7nw%3D%3D</t>
-  </si>
-  <si>
-    <t>179-UJ2-B-HR-G-TH</t>
-  </si>
-  <si>
-    <t>UJ2-B-HR-G-TH</t>
-  </si>
-  <si>
     <t>PKM22EPPH4001-B0 Buzzer</t>
   </si>
   <si>
@@ -303,24 +294,6 @@
     <t>Resettable fuse Ihold=1.1A, Itrip=2.2A, trip time 6.6s, max. 40 A, 30 V radial</t>
   </si>
   <si>
-    <t>UJ2-B-HR-G-TH USB B Port</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/Vishay-BC-Components/K104K15X7RF5WH5?qs=sGAEpiMZZMuMW9TJLBQkXstS33ZYjGCMau7NPGXn%2F5U%3D</t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
-    <t>K104K15X7RF5WH5</t>
-  </si>
-  <si>
-    <t>594-K104K15X7RF5WH5</t>
-  </si>
-  <si>
-    <t>Ceramic Capacitor 0.1uF</t>
-  </si>
-  <si>
     <t>Electrolytic Capacitor 10uF</t>
   </si>
   <si>
@@ -387,21 +360,6 @@
     <t>https://www.reichelt.de/de/de/shop/produkt/subminiatur-elko_radial_1_0_f_63_v_rm_1_5_85_c_1000h_20_-18162</t>
   </si>
   <si>
-    <t>Push Button</t>
-  </si>
-  <si>
-    <t>https://www.mouser.de/ProductDetail/TE-Connectivity-PB/2-1977223-8?qs=WwRK9Mn48WC%252B3bZnlicO2g%3D%3D</t>
-  </si>
-  <si>
-    <t>506-2-1977223-8</t>
-  </si>
-  <si>
-    <t>2-1977223-8</t>
-  </si>
-  <si>
-    <t>TE Connectivity</t>
-  </si>
-  <si>
     <t>330 uH Inductor</t>
   </si>
   <si>
@@ -415,6 +373,48 @@
   </si>
   <si>
     <t>https://www.mouser.de/ProductDetail/Coilcraft/RFC0810B-334KE?qs=ZYnrCdKdyedaHxMGgKKlpw%3D%3D</t>
+  </si>
+  <si>
+    <t>Push Button TS02-66-60-BK-260-LCR-D</t>
+  </si>
+  <si>
+    <t>TS02-66-60-BK-260-LCR-D</t>
+  </si>
+  <si>
+    <t>179-TS026660BK260LCR</t>
+  </si>
+  <si>
+    <t>https://www.mouser.de/ProductDetail/Same-Sky/TS02-66-60-BK-260-LCR-D?qs=A6eO%252BMLsxmQnLv1ZYEDDrQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Epcos</t>
+  </si>
+  <si>
+    <t>100nF Ceramic-Chip Capacitors</t>
+  </si>
+  <si>
+    <t>1N5908</t>
+  </si>
+  <si>
+    <t>TVS Diode 5V,</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>https://www.mouser.de/ProductDetail/STMicroelectronics/1N5908?qs=YstF3%2FqpSF%252BhnZj98fb9oQ%3D%3D&amp;srsltid=AfmBOorzoElHmplEbmoCVDHx7_FNw26QDkjH7mLPxjuBH2CioThL0RCf</t>
+  </si>
+  <si>
+    <t>GCT</t>
+  </si>
+  <si>
+    <t>USB3145-30-1-A</t>
+  </si>
+  <si>
+    <t>640-USB3145-30-1-A</t>
+  </si>
+  <si>
+    <t>https://www.mouser.de/ProductDetail/GCT/USB3145-30-1-A?qs=KUoIvG%2F9IlYD1lvSRu5iyg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -701,7 +701,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -817,14 +817,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -841,6 +833,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -893,10 +889,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1204,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1289,7 +1281,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40">
+      <c r="A5" s="38">
         <v>1</v>
       </c>
       <c r="B5" s="19">
@@ -1322,7 +1314,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="41">
+      <c r="A6" s="39">
         <v>2</v>
       </c>
       <c r="B6" s="23">
@@ -1355,7 +1347,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41">
+      <c r="A7" s="39">
         <v>3</v>
       </c>
       <c r="B7" s="23">
@@ -1365,7 +1357,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>45</v>
@@ -1394,11 +1386,11 @@
       <c r="B8" s="24">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="36" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E8" s="30">
         <v>2477</v>
@@ -1406,7 +1398,7 @@
       <c r="F8" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="37" t="s">
         <v>57</v>
       </c>
       <c r="H8" s="32">
@@ -1431,7 +1423,7 @@
         <v>56</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E9" s="24" t="s">
         <v>54</v>
@@ -1461,13 +1453,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>29</v>
@@ -1483,7 +1475,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1494,29 +1486,29 @@
         <v>1</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="H11" s="34">
-        <v>1.29</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="I11" s="33">
-        <f>B11*H11</f>
-        <v>1.29</v>
+        <f t="shared" ref="I11" si="1">B11*H11</f>
+        <v>0.66200000000000003</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1530,7 +1522,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>62</v>
@@ -1590,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>72</v>
@@ -1612,93 +1604,84 @@
       </c>
       <c r="I14" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J14" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
+    <row r="15" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="26">
+        <v>2</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B16" s="26">
         <v>1</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C16" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="26" t="s">
+      <c r="D16" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F16" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G16" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H16" s="34">
         <v>5.16</v>
       </c>
-      <c r="I15" s="33">
-        <f t="shared" ref="I15:I21" si="1">B15*H15</f>
+      <c r="I16" s="33">
+        <f t="shared" ref="I16:I22" si="2">B16*H16</f>
         <v>5.16</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J16" s="35" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+    <row r="17" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
         <v>12</v>
       </c>
-      <c r="B16" s="27">
-        <v>4</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="36">
-        <v>0.13</v>
-      </c>
-      <c r="I16" s="33">
-        <f t="shared" si="1"/>
-        <v>0.52</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
-        <v>13</v>
-      </c>
       <c r="B17" s="26">
-        <v>2</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>96</v>
+        <v>3</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F17" s="26" t="s">
         <v>29</v>
@@ -1710,28 +1693,28 @@
         <v>0.11</v>
       </c>
       <c r="I17" s="33">
-        <f t="shared" si="1"/>
-        <v>0.22</v>
+        <f t="shared" si="2"/>
+        <v>0.33</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="26">
         <v>1</v>
       </c>
-      <c r="C18" s="42" t="s">
-        <v>96</v>
+      <c r="C18" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>29</v>
@@ -1743,28 +1726,28 @@
         <v>0.26</v>
       </c>
       <c r="I18" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.26</v>
       </c>
       <c r="J18" s="35" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="6">
-        <v>15</v>
+      <c r="A19" s="7">
+        <v>14</v>
       </c>
       <c r="B19" s="26">
         <v>1</v>
       </c>
-      <c r="C19" s="42" t="s">
-        <v>96</v>
+      <c r="C19" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>29</v>
@@ -1776,25 +1759,25 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="I19" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="26">
         <v>1</v>
       </c>
-      <c r="C20" s="42" t="s">
-        <v>96</v>
+      <c r="C20" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="26" t="s">
@@ -1807,340 +1790,350 @@
         <v>0.02</v>
       </c>
       <c r="I20" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
       <c r="J20" s="35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="26">
-        <v>1</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>108</v>
+        <v>6</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>117</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>107</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E21" s="27"/>
       <c r="F21" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="26">
-        <v>498</v>
-      </c>
-      <c r="H21" s="34">
-        <v>0.06</v>
-      </c>
-      <c r="I21" s="33">
-        <f t="shared" si="1"/>
-        <v>0.06</v>
-      </c>
-      <c r="J21" s="35" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
-        <v>18</v>
+      <c r="G21" s="26"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="35"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
+        <v>17</v>
       </c>
       <c r="B22" s="26">
         <v>1</v>
       </c>
-      <c r="C22" s="42" t="s">
-        <v>108</v>
+      <c r="C22" s="40" t="s">
+        <v>99</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F22" s="26" t="s">
         <v>29</v>
       </c>
       <c r="G22" s="26">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H22" s="34">
         <v>0.06</v>
       </c>
       <c r="I22" s="33">
-        <f t="shared" ref="I22:I25" si="2">B22*H22</f>
+        <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="J22" s="35" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="26">
         <v>1</v>
       </c>
-      <c r="C23" s="42" t="s">
-        <v>108</v>
+      <c r="C23" s="40" t="s">
+        <v>99</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="26">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="H23" s="34">
         <v>0.06</v>
       </c>
       <c r="I23" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I23:I26" si="3">B23*H23</f>
         <v>0.06</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
+        <v>19</v>
+      </c>
+      <c r="B24" s="26">
+        <v>1</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="26">
+        <v>471</v>
+      </c>
+      <c r="H24" s="34">
+        <v>0.06</v>
+      </c>
+      <c r="I24" s="33">
+        <f t="shared" si="3"/>
+        <v>0.06</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="7">
         <v>20</v>
       </c>
-      <c r="B24" s="42">
-        <v>1</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="H24" s="34">
-        <v>0.16</v>
-      </c>
-      <c r="I24" s="33">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="J24" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
-        <v>21</v>
-      </c>
-      <c r="B25" s="26">
-        <v>1</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>122</v>
+      <c r="B25" s="40">
+        <v>2</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>113</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="H25" s="34">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="I25" s="33">
+        <f t="shared" si="3"/>
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="J25" s="35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>21</v>
+      </c>
+      <c r="B26" s="26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="34">
         <v>1.26</v>
       </c>
-      <c r="I25" s="33">
-        <f t="shared" si="2"/>
+      <c r="I26" s="33">
+        <f t="shared" si="3"/>
         <v>1.26</v>
       </c>
-      <c r="J25" s="35" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
+      <c r="J26" s="35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
         <v>22</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="35"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G28" s="58" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="35"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G29" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="H28" s="58"/>
-      <c r="I28" s="10">
-        <f>SUM(I5:I26)</f>
-        <v>23.364999999999998</v>
-      </c>
-      <c r="J28" s="61"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="H29" s="58"/>
+      <c r="I29" s="10">
+        <f>SUM(I5:I27)</f>
+        <v>22.038999999999998</v>
+      </c>
+      <c r="J29" s="42"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="G29" s="59" t="s">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="G30" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="H29" s="59"/>
-      <c r="I29" s="8">
-        <f>I28*0.19</f>
-        <v>4.4393500000000001</v>
-      </c>
-      <c r="J29" s="61"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="53" t="s">
+      <c r="H30" s="59"/>
+      <c r="I30" s="8">
+        <f>I29*0.19</f>
+        <v>4.1874099999999999</v>
+      </c>
+      <c r="J30" s="42"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="54"/>
-      <c r="C30" s="14" t="s">
+      <c r="B31" s="54"/>
+      <c r="C31" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="54" t="s">
+      <c r="D31" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="G30" s="59" t="s">
+      <c r="E31" s="55"/>
+      <c r="G31" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="H30" s="59"/>
-      <c r="I30" s="9">
-        <f>I28*1.19</f>
-        <v>27.804349999999996</v>
-      </c>
-      <c r="J30" s="61"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="48"/>
-      <c r="I31" s="60"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="9">
+        <f>I29*1.19</f>
+        <v>26.226409999999998</v>
+      </c>
+      <c r="J31" s="42"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="44"/>
       <c r="C32" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E32" s="48"/>
+      <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="44"/>
       <c r="C33" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="48"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="44"/>
+      <c r="C34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="48"/>
-      <c r="H33" t="s">
+      <c r="E34" s="48"/>
+      <c r="H34" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="50"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="46"/>
+      <c r="C35" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="50"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="49" t="s">
+      <c r="B36" s="46"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="50"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
+      <c r="E36" s="50"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="2"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="3"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+      <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2151,7 +2144,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="2"/>
       <c r="G53" s="1"/>
@@ -2163,7 +2156,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="1"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="1"/>
       <c r="F54" s="2"/>
       <c r="G54" s="1"/>
@@ -2174,7 +2167,7 @@
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
+      <c r="C55" s="2"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="2"/>
@@ -2186,7 +2179,7 @@
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="2"/>
+      <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="2"/>
@@ -2207,48 +2200,65 @@
       <c r="I57" s="1"/>
       <c r="J57" s="3"/>
     </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="G28:H28"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="D34:E34"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F26" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$A$31:$A$35</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F26:F27 F5:F10 F12:F24" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>$A$32:$A$36</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F25" xr:uid="{75F82313-0372-4483-9899-AEAC29E1E112}">
+      <formula1>$A$29:$A$33</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{2C71D0E7-017E-4287-87F6-E3AC4A9F966D}">
+      <formula1>$A$27:$A$31</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D32" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D31" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D34" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D34" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D33" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D32" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D35" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="C8" r:id="rId5" display="https://www.mouser.de/manufacturer/keystone/" xr:uid="{B1F4DA8D-BD2D-43B5-89B1-25ABF1C0529C}"/>
     <hyperlink ref="J7" r:id="rId6" xr:uid="{4987D0AF-D5AF-4E59-98D4-4D42395D39EC}"/>
     <hyperlink ref="J6" r:id="rId7" xr:uid="{9F9E23C2-0CE5-4F54-A453-2FB0482436B8}"/>
     <hyperlink ref="J5" r:id="rId8" xr:uid="{98A04EE6-D62B-4687-AC62-05CBC3BC7F14}"/>
-    <hyperlink ref="J11" r:id="rId9" xr:uid="{E0F5E5CE-E58B-4232-8792-169F1500BA12}"/>
-    <hyperlink ref="J12" r:id="rId10" xr:uid="{85611FA3-DA6B-4401-BC4A-CB8B8F5F9061}"/>
+    <hyperlink ref="J12" r:id="rId9" xr:uid="{85611FA3-DA6B-4401-BC4A-CB8B8F5F9061}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId10"/>
   <headerFooter>
     <oddHeader>&amp;CParts list
 Practical Electronics</oddHeader>

--- a/schematic-design/Partslist_Group_PE04_2 - With HSRW.xlsx
+++ b/schematic-design/Partslist_Group_PE04_2 - With HSRW.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\pe04\schematic-design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEBE582-9EB0-4947-90E2-B5CA8B45C980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831B8F7C-A46F-4548-AEF4-EB4814D2FC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-10800" yWindow="6720" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parts" sheetId="5" r:id="rId1"/>
@@ -396,9 +396,6 @@
     <t>1N5908</t>
   </si>
   <si>
-    <t>TVS Diode 5V,</t>
-  </si>
-  <si>
     <t>ST</t>
   </si>
   <si>
@@ -415,6 +412,9 @@
   </si>
   <si>
     <t>https://www.mouser.de/ProductDetail/GCT/USB3145-30-1-A?qs=KUoIvG%2F9IlYD1lvSRu5iyg%3D%3D</t>
+  </si>
+  <si>
+    <t>TVS Diode 5V</t>
   </si>
 </sst>
 </file>
@@ -837,45 +837,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -889,6 +850,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1215,38 +1215,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="52"/>
+      <c r="B1" s="48"/>
       <c r="C1" s="17" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="52"/>
+      <c r="B2" s="48"/>
       <c r="C2" s="18" t="s">
         <v>49</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1486,19 +1486,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>124</v>
-      </c>
       <c r="E11" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" s="34">
         <v>0.66200000000000003</v>
@@ -1508,7 +1508,7 @@
         <v>0.66200000000000003</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1616,10 +1616,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>119</v>
@@ -1631,7 +1631,7 @@
       <c r="H15" s="34"/>
       <c r="I15" s="33"/>
       <c r="J15" s="35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1999,10 +1999,10 @@
       <c r="J27" s="35"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G29" s="58" t="s">
+      <c r="G29" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H29" s="58"/>
+      <c r="H29" s="45"/>
       <c r="I29" s="10">
         <f>SUM(I5:I27)</f>
         <v>22.038999999999998</v>
@@ -2017,10 +2017,10 @@
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
-      <c r="G30" s="59" t="s">
+      <c r="G30" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="H30" s="59"/>
+      <c r="H30" s="46"/>
       <c r="I30" s="8">
         <f>I29*0.19</f>
         <v>4.1874099999999999</v>
@@ -2028,21 +2028,21 @@
       <c r="J30" s="42"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="54"/>
+      <c r="B31" s="50"/>
       <c r="C31" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="55"/>
-      <c r="G31" s="59" t="s">
+      <c r="E31" s="53"/>
+      <c r="G31" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="59"/>
+      <c r="H31" s="46"/>
       <c r="I31" s="9">
         <f>I29*1.19</f>
         <v>26.226409999999998</v>
@@ -2050,71 +2050,71 @@
       <c r="J31" s="42"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="44"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="47" t="s">
+      <c r="D32" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="48"/>
+      <c r="E32" s="57"/>
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="44"/>
+      <c r="B33" s="52"/>
       <c r="C33" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="48"/>
+      <c r="E33" s="57"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="44"/>
+      <c r="B34" s="52"/>
       <c r="C34" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="47" t="s">
+      <c r="D34" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="48"/>
+      <c r="E34" s="57"/>
       <c r="H34" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="45" t="s">
+      <c r="A35" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="46"/>
+      <c r="B35" s="55"/>
       <c r="C35" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="49" t="s">
+      <c r="D35" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="50"/>
+      <c r="E35" s="59"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="46"/>
+      <c r="B36" s="55"/>
       <c r="C36" s="16"/>
-      <c r="D36" s="49" t="s">
+      <c r="D36" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="50"/>
+      <c r="E36" s="59"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
@@ -2214,16 +2214,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D31:E31"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A36:B36"/>
@@ -2233,6 +2223,16 @@
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="D35:E35"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
